--- a/templates/系统数据模板.xlsx
+++ b/templates/系统数据模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2007-加班申请" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="码表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2007-加班申请" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="码表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,26 +26,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000071E3"/>
-        <bgColor rgb="000071E3"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,29 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E5E5E5"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E5E5E5"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E5E5E5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E5E5E5"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,182 +414,402 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13.2" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>中文名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>工号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>开始时间</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>定额量</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>加班报酬类型</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>加班原因</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>选项值</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>T556P</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>T555R</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>是否必填</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>填报说明</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>使用新方案的8位数字工号</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>此字段作为校验字段，如与个人基本信息内姓名不一致，导入会报错</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YYYYMMDD格式</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>YYYYMMDD格式</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HHMM格式</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>HHMM格式</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>时数</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>自由填写</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>取值举例</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>163161</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>谭文杰</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20200101</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20200101</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3 补休</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>序列号</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RP50G-PERNR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P2007-BEGDA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P2007-ENDDA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>P2007-KTART</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>P2007-BEGUZ</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P2007-ENDUZ</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>P2007-ANZHL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>P2007-VERSL</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>RESON</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10010001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>20260801</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>20260801</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>00151177</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>童辉武</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>10 已核准的加班</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>1 支付加班费</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>产能爬坡</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>生产一线早班统一加班生产</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10010002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>20260802</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20260802</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>00151177</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>童辉武</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>10 已核准的加班</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>1 支付加班费</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>设备检修</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>生产一线早班统一加班生产</t>
         </is>
       </c>
     </row>
